--- a/data/entreprises.xlsx
+++ b/data/entreprises.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_disallowed</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1088,9 +1088,21 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3 employés</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>contact@braindcode.com</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.braindcode.com/recrutement</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/braindcode/</t>
@@ -1108,7 +1120,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1152,11 @@
           <t>recrutement@aisysnext.com</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://aisysnext.com/opportunites-jobs-offre/</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/aisysnext/</t>
@@ -1158,7 +1174,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1220,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1274,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1316,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1362,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1412,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1454,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1500,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1542,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1588,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1638,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1684,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1730,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1740,9 +1756,21 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1 COLLABORATEURS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>contact@tunisys.com.tn</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.tunisys.com.tn/careers/</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/tunisys/</t>
@@ -1760,7 +1788,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1842,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1888,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1938,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1980,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2030,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2062,11 @@
           <t>info@innoway-solutions.com</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.innoway-solutions.com/careers</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/innoway/</t>
@@ -2052,7 +2084,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2134,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2180,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2234,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2284,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2330,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2357,11 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>contact@zembratech.com</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
@@ -2344,7 +2380,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2416,11 @@
           <t>recrutment.fejja@sebn.com</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.sebn.com/en/career/</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/sebn-tn-2/</t>
@@ -2398,7 +2438,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2488,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2534,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2580,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2611,11 @@
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>contact@citygo.tn</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
@@ -2590,7 +2634,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2680,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2726,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2780,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2822,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2868,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2900,11 @@
           <t>contact@sbmtunisie.com</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>http://www.sbm-tunisie.com/postes/</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/sbm/</t>
@@ -2874,7 +2922,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2968,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -2947,8 +2995,16 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>contact@s-mecatron.com</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.s-mecatron.com/recrutements/</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/s-mecatron/</t>
@@ -2966,7 +3022,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3068,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3118,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3164,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3206,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3256,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3302,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3352,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3398,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3444,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3471,11 @@
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>info@my-domain.com</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
@@ -3434,7 +3494,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3536,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3586,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3632,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3678,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3724,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3756,11 @@
           <t>contact@attoset.com</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.attoset.com/about#careers</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/attoset/</t>
@@ -3714,7 +3778,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3810,11 @@
           <t>rh@opto.tn</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.opto.tn/career</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2026/opto/</t>
@@ -3764,7 +3832,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3878,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3932,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3982,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -3964,7 +4032,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4074,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4174,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4137,8 +4205,16 @@
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>contact@uptech.com.tn</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://uptech.com.tn/carriere.html</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/uptech/</t>
@@ -4156,7 +4232,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4282,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4328,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4378,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4424,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4470,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4520,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4566,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4612,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4662,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -4612,13 +4688,21 @@
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>75 Collaborateurs</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>recrutement@st2i.com.tn</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>http://www.st2i.com.tn/?cat=52</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/st2i/</t>
@@ -4636,7 +4720,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4756,11 @@
           <t>recrutement@itserv.tn</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://itserv.tn/carrieres-it-en-tunisie/</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/it-serv/</t>
@@ -4690,7 +4778,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4824,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4856,11 @@
           <t>internships@looyas.com</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.looyas.com/join-us/</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/looyas/</t>
@@ -4786,7 +4878,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4906,11 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://mass-analytics.com/about/mass-analytics-marketing-mix-modeling-careers/</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/mass-analytics/</t>
@@ -4832,7 +4928,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4974,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4924,7 +5020,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5062,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -4998,7 +5094,11 @@
           <t>career@enosis.ma</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://enosis.ma/jobs</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/enosis/</t>
@@ -5016,7 +5116,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5162,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5204,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5250,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5300,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5354,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5400,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5446,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5373,8 +5473,16 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>hello@digitalfriendly.agency</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://digitalfriendly.agency/carriere/</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/digital-friendly-agency/</t>
@@ -5392,7 +5500,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5554,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5604,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5654,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_disallowed</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5681,11 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>contact@samkraft.com</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
@@ -5592,7 +5704,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5754,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5780,11 @@
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0 Personnes</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>stage@mpbs.com.tn</t>
@@ -5692,7 +5808,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5854,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5896,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5942,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -5857,8 +5973,16 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>contact@etctn.com</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://etctn.com/careers/</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/etc/</t>
@@ -5876,7 +6000,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5926,7 +6050,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -5976,7 +6100,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6154,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6204,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6250,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6296,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6328,11 @@
           <t>rh@ia-tech.net</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://ia-tech.net/career/</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/iat/</t>
@@ -6222,7 +6350,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6404,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6430,11 @@
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>50 collaborateurs</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>contact@sierrabravointelligence.com</t>
@@ -6326,7 +6458,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6484,11 @@
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>50 collaborateurs</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>contact@amazedit.fr</t>
@@ -6376,7 +6512,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6558,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6608,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6658,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6708,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6754,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6808,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6854,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6881,11 @@
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>contact@summitriseit.com</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
@@ -6764,7 +6904,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6950,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6986,11 @@
           <t>jobs@numeryx.fr</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.numeryx.fr/carriere</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/numeryx/</t>
@@ -6864,7 +7008,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6900,7 +7044,11 @@
           <t>info@bellamine-industries.com</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>http://www.bellamine-industries.com/Pages/recrutement/recrutement.html</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/bellamine-industries-moditec/</t>
@@ -6918,7 +7066,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -6964,7 +7112,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7162,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7212,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7244,11 @@
           <t>contact@theshapers.co</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://theshapers.co/programs/career-transition/</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/shape-your-future/</t>
@@ -7114,7 +7266,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7316,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7366,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7240,13 +7392,21 @@
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0 COLLABORATEURS</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>contact@siryos.com</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://siryos.com/fr/carrieres</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/siryos/</t>
@@ -7264,7 +7424,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7474,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7524,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7574,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7620,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7652,11 @@
           <t>careers@smartovate.com</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.smartovate.com/en/jobs</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/smartovate/</t>
@@ -7510,7 +7674,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7720,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7766,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7812,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7858,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7900,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7946,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7996,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -7882,7 +8046,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -7932,7 +8096,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -7978,7 +8142,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8188,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_disallowed</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8224,11 @@
           <t>internships@linsoft.com</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.linsoft.com/en/careers</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/linsoft/</t>
@@ -8078,7 +8246,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8296,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8346,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8392,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8438,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8488,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8538,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8565,11 @@
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>commercial@inter-gts.com</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
@@ -8416,7 +8588,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8630,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8676,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8726,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8780,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8830,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8880,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8912,11 @@
           <t>contact@defendr.gg</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://defendr.gg/en/jobs</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/defendr/</t>
@@ -8758,7 +8934,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8976,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -8831,7 +9007,11 @@
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>info@mysite.com</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
@@ -8850,7 +9030,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8886,7 +9066,11 @@
           <t>internship@itempire-group.com</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.itempire-group.com/carriere/</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/it-empire/</t>
@@ -8904,7 +9088,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -8958,7 +9142,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9188,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9234,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9280,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9316,11 @@
           <t>recrutement@comar.tn</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.comar.tn/recrutement</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/comar/</t>
@@ -9150,7 +9338,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9388,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9438,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9488,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9534,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9580,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9626,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9668,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9700,11 @@
           <t>contact@pixiimotors.com</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://pixiimotors.com/career</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/pixii-motors/</t>
@@ -9530,7 +9722,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9772,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9606,13 +9798,21 @@
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0+ Employees</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t>jobs-maghreb@scheidt-bachmann.de</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://www.scheidt-bachmann.de/en/career/working-culture</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/scheidt-bachmann/</t>
@@ -9630,7 +9830,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9862,11 @@
           <t>contact@siv.games</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://siv.games/video-game-jobs/</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/siv-games/</t>
@@ -9680,7 +9884,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9930,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9980,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -9818,7 +10022,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9868,7 +10072,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -9900,7 +10104,11 @@
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.azurex.net/jobs/</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/azurex/</t>
@@ -9918,7 +10126,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -9945,7 +10153,11 @@
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>hello@it-grow.tn</t>
+        </is>
+      </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
@@ -9964,7 +10176,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10226,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10276,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10326,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_disallowed</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10380,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10426,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10472,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10514,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10546,11 @@
           <t>careers@trustdev.info</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.trustdev.info/careers/</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/trustdev/</t>
@@ -10352,7 +10568,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10604,11 @@
           <t>recrutement@aymax.fr</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://aymax.fr/recrutement-aymax/</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/aymax/</t>
@@ -10406,7 +10626,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10676,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10730,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10780,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10826,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10872,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10922,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10972,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10794,7 +11014,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -10822,7 +11042,11 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/tn/en/careers.html</t>
+        </is>
+      </c>
       <c r="I216" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/kpmg-2/</t>
@@ -10840,7 +11064,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -10886,7 +11110,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -10936,7 +11160,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -10986,7 +11210,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11256,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11306,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11356,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11406,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11452,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11502,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11548,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11594,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11640,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11690,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11736,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11768,11 @@
           <t>hr@pearls.consulting</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://pearls.consulting/careers/</t>
+        </is>
+      </c>
       <c r="I231" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/pearls/</t>
@@ -11562,7 +11790,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11832,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11860,11 @@
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://recrutement.attijaribank.com.tn/</t>
+        </is>
+      </c>
       <c r="I233" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/attijari-bank/</t>
@@ -11650,7 +11882,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11932,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11978,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11792,7 +12024,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11834,7 +12066,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11866,7 +12098,11 @@
           <t>stages@excellia.tn</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://excellia.tn/carriere/</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/excellia-solutions/</t>
@@ -11884,7 +12120,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -11926,7 +12162,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -11972,7 +12208,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12244,11 @@
           <t>jobs@alight.eu</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://alightmea.com/career/key-values-and-culture/</t>
+        </is>
+      </c>
       <c r="I241" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/alight-mea/</t>
@@ -12026,7 +12266,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12292,11 @@
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>70 collaborateurs</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
           <t>rh@x-tern.com</t>
@@ -12076,7 +12320,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12366,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12398,11 @@
           <t>stages-sousse@hutchinson.com</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://www.hutchinson.com/fr/carriere</t>
+        </is>
+      </c>
       <c r="I244" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/hutchinson/</t>
@@ -12172,7 +12420,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12470,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12516,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12546,11 @@
           <t>Nabeul</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>0 Collaborateurs</t>
+        </is>
+      </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
@@ -12318,7 +12570,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12612,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12662,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12712,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12762,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12812,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12862,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12912,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12966,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12764,7 +13016,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12810,7 +13062,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -12864,7 +13116,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12892,7 +13144,11 @@
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://careers.societegenerale.com/jobs-etudiants</t>
+        </is>
+      </c>
       <c r="I259" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/societe-generale-ats/</t>
@@ -12910,7 +13166,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13212,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -12998,7 +13254,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13304,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13350,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13392,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13438,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13209,8 +13465,16 @@
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>info@autoelectric.com</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://www.autoelectric.com/de/karriere/stellenangebote</t>
+        </is>
+      </c>
       <c r="I266" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/nexans-autoelectric/</t>
@@ -13228,7 +13492,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13546,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13592,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13620,11 @@
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://pursuitaero.com/careers</t>
+        </is>
+      </c>
       <c r="I269" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/pursuit-aerospace/</t>
@@ -13374,7 +13642,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13692,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13746,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13792,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13842,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13888,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13647,8 +13915,16 @@
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>contact@matineconsulting.com</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://www.matineconsulting.com/careers/</t>
+        </is>
+      </c>
       <c r="I275" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/matine-consulting/</t>
@@ -13666,7 +13942,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13988,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13762,7 +14038,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13789,7 +14065,11 @@
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>info@sttp-transformation.com</t>
+        </is>
+      </c>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
@@ -13808,7 +14088,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -13854,7 +14134,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13900,7 +14180,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13942,7 +14222,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -13988,7 +14268,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14038,7 +14318,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -14092,7 +14372,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14414,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14460,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14502,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14544,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14590,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14632,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14394,7 +14674,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14716,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14762,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14528,7 +14808,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14858,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14904,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14950,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14992,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14762,7 +15042,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -14804,7 +15084,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14854,7 +15134,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14900,7 +15180,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14942,7 +15222,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -14984,7 +15264,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15310,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -15076,7 +15356,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15398,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15430,11 @@
           <t>stages@hydatis.fr</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://www.hydatis.com/careers/</t>
+        </is>
+      </c>
       <c r="I308" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/hydatis/</t>
@@ -15168,7 +15452,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -15210,7 +15494,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15540,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15568,11 @@
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://cognira.com/careers/</t>
+        </is>
+      </c>
       <c r="I311" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/cognira/</t>
@@ -15302,7 +15590,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -15344,7 +15632,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15682,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15724,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15766,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15520,7 +15808,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15850,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15892,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15646,7 +15934,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15984,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -15742,7 +16030,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -15788,7 +16076,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15830,7 +16118,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15876,7 +16164,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15922,7 +16210,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16252,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -15992,7 +16280,11 @@
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://www.sopal.com/carriere</t>
+        </is>
+      </c>
       <c r="I327" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/sopal/</t>
@@ -16010,7 +16302,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16356,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16398,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16148,7 +16440,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16194,7 +16486,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16528,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16566,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16612,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -16362,7 +16654,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16692,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16415,7 +16707,11 @@
           <t>Développement Web &amp; Mobile</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Découvrez les offres et forfaits mobiles et internet de Orange.tn l'opérateur téléphonique numéro un en Tunisie. Profitez du meilleur réseau partout en Tunisie</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
           <t>http://www.orange.tn/</t>
@@ -16428,7 +16724,11 @@
           <t>recrutement@orange.com.tn</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://www.orange.tn/carrieres</t>
+        </is>
+      </c>
       <c r="I337" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/orange/</t>
@@ -16446,7 +16746,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16784,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16799,11 @@
           <t>Design &amp; Expérience Utilisateur</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Devwise est une agence digitale à Nabeul spécialisée en développement web, applications mobiles, IA, cloud, design UI/UX et business intelligence. Découvrez notre équipe et nos partenaires.</t>
+        </is>
+      </c>
       <c r="D339" t="inlineStr">
         <is>
           <t>http://www.devwise.tn/</t>
@@ -16512,7 +16816,11 @@
           <t>contact@devwise.tn</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://www.devwise.tn/offres/emploi</t>
+        </is>
+      </c>
       <c r="I339" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/devwise/</t>
@@ -16530,7 +16838,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16876,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16918,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16933,11 @@
           <t>Design &amp; Expérience Utilisateur</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>From strategy to execution, we guide organizations through transformation, bringing clarity to complexity and supporting growth at every stage.</t>
+        </is>
+      </c>
       <c r="D342" t="inlineStr">
         <is>
           <t>https://www.binitns.com/</t>
@@ -16656,7 +16968,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16698,7 +17010,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16740,7 +17052,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16782,7 +17094,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16797,7 +17109,11 @@
           <t>Design &amp; Expérience Utilisateur</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Develop your skills with our training in AI, data science, data analysis, Web, UX/UI, and software testing in Tunisia.</t>
+        </is>
+      </c>
       <c r="D346" t="inlineStr">
         <is>
           <t>http://www.softyskills.com/</t>
@@ -16828,7 +17144,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16843,7 +17159,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>SMOFT ERP est une solution ERP Cloud complète pour gérer votre entreprise avec CRM, finance, RH, production, logistique et automatisation IA.</t>
+        </is>
+      </c>
       <c r="D347" t="inlineStr">
         <is>
           <t>http://www.smoft.io/</t>
@@ -16851,8 +17171,16 @@
       </c>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>contact@smoft.tn</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://smoft.io/fr/carriere</t>
+        </is>
+      </c>
       <c r="I347" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/smoft/</t>
@@ -16870,7 +17198,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -16912,7 +17240,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=fetch_error</t>
         </is>
       </c>
     </row>
@@ -16950,7 +17278,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -16996,7 +17324,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17366,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17408,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17095,7 +17423,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Relead aide les annonceurs à atteindre leurs publics cibles via la publicité Wi-Fi et monétiser les points d’accès Wi-Fi de son réseau de partenaires.</t>
+        </is>
+      </c>
       <c r="D353" t="inlineStr">
         <is>
           <t>http://www.relead.tn/</t>
@@ -17103,7 +17435,11 @@
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>contact@relead.tn</t>
+        </is>
+      </c>
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
@@ -17122,7 +17458,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17473,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>The most powerful, simple and trusted way to gather experience data. Start your journey to experience management and try a free account today.</t>
+        </is>
+      </c>
       <c r="D354" t="inlineStr">
         <is>
           <t>https://globaleysurvey.ey.com/jfe/form/SV_1UmuVxlg6kmBg4m</t>
@@ -17164,7 +17504,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17542,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17557,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>A global leader in consulting, technology services and digital transformation, we offer an array of integrated services combining technology with deep sector expertise.</t>
+        </is>
+      </c>
       <c r="D356" t="inlineStr">
         <is>
           <t>https://www.capgemini.com/</t>
@@ -17226,7 +17570,11 @@
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/careers/</t>
+        </is>
+      </c>
       <c r="I356" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/capgemini/</t>
@@ -17244,7 +17592,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17286,7 +17634,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17676,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17343,20 +17691,32 @@
           <t>Design &amp; Expérience Utilisateur</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Partner with a leading lending software provider that offers innovative banking solutions to transform and automate financial operations.</t>
+        </is>
+      </c>
       <c r="D359" t="inlineStr">
         <is>
           <t>http://www.axefinance.com/</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>0 + Employees</t>
+        </is>
+      </c>
       <c r="G359" t="inlineStr">
         <is>
           <t>hr@axefinance.com</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://www.axefinance.com/company/careers/</t>
+        </is>
+      </c>
       <c r="I359" t="inlineStr">
         <is>
           <t>https://pfebooks.com/catalogue/2025/axe-finance/</t>
@@ -17374,7 +17734,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17776,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17458,7 +17818,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17856,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17538,7 +17898,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17913,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Tech-Expert conçoit, développe et industrialise des solutions digitales à fort impact business pour des organisations en pleine évolution.</t>
+        </is>
+      </c>
       <c r="D364" t="inlineStr">
         <is>
           <t>http://www.tech-expert.io/</t>
@@ -17584,7 +17948,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17599,7 +17963,11 @@
           <t>Développement Web &amp; Mobile</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>The form can't receive new submissions at this moment.</t>
+        </is>
+      </c>
       <c r="D365" t="inlineStr">
         <is>
           <t>https://tally.so/r/3jOxk4</t>
@@ -17626,7 +17994,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17668,7 +18036,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17683,7 +18051,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>#1 LegalTech platform in MENA. Create, sign &amp; manage contracts online. Get instant legal advice &amp; secure operations with our innovative SaaS solution.</t>
+        </is>
+      </c>
       <c r="D367" t="inlineStr">
         <is>
           <t>http://www.e-tafakna.com/</t>
@@ -17710,7 +18082,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17725,7 +18097,11 @@
           <t>Business &amp; Entrepreneuriat</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Hanoutik est une suite logicielle tout-en-un pour les commerçants détaillants, les grossistes fournisseurs et les consommateurs en Tunisie.</t>
+        </is>
+      </c>
       <c r="D368" t="inlineStr">
         <is>
           <t>http://www.hanoutik.com/</t>
@@ -17756,7 +18132,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17794,7 +18170,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17836,7 +18212,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=robots_unreachable</t>
         </is>
       </c>
     </row>
@@ -17851,7 +18227,11 @@
           <t>Design &amp; Expérience Utilisateur</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Infotech Consulting Services (ICS) offre une intégration de solutions qui fournit une large gamme d'applications commerciales faciles à utiliser, donnant aux entreprises un accès facile aux logiciels qu'elles peuvent utiliser pour gérer et développer leur entreprise.</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr">
         <is>
           <t>https://ics-tunisie.com/</t>
@@ -17882,7 +18262,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=ok</t>
         </is>
       </c>
     </row>
@@ -17924,7 +18304,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -17966,7 +18346,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18388,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18050,7 +18430,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18092,7 +18472,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18130,7 +18510,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18548,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18206,7 +18586,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18624,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18282,7 +18662,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18700,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18738,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18776,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18814,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18852,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18890,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
@@ -18548,7 +18928,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>enrichissement=not_attempted</t>
+          <t>enrichissement=no_website</t>
         </is>
       </c>
     </row>
